--- a/scenarios/S01_enterprise_architecture/deliverables/TCO_벤더평가_시트.xlsx
+++ b/scenarios/S01_enterprise_architecture/deliverables/TCO_벤더평가_시트.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TCO비교" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="벤더평가" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DB선정체크리스트" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RTM" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -580,7 +581,6 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -640,7 +640,6 @@
           <t>별도취득</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -778,7 +777,6 @@
       <c r="E5" t="n">
         <v>7</v>
       </c>
-      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -983,4 +981,760 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>req_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>일시</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>요청자</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>소스</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>결정</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>요약</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>영향 산출물</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>변경유형</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>DA점수</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>위키 커밋</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>REQ-20250214-cto-ai-architecture-approval-update</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-07-31T21:00:03.286+09:00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CTO실</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>bench:S01:B00000</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>비교·선정안과 관련 산출물 업데이트를 승인한다. 단, 최종 아키텍처 확정 전 비용·성능 가정, 평가 가중치, 컴플라이언스 통제, 라이선스·운영 책임 및 PoC 성공 기준을 보완·확정한다.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>AWS·Azure·GCP 클라우드, GPU Serving 자체구축·클라우드 임차, SAP HANA·Oracle DB를 비교하고 CTO 의사결정 및 요구사항 추적을 갱신한다.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>전사 AI 아키텍처 비교·선정안; AI Serving 하드웨어 검토서; 데이터베이스 선정 검토서; CTO실 의사결정 보고서; 산출물_설계서.docx; 요구사항_추적표.xlsx; 보고_장표.pptx</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>add,modify</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/3d98b933eab01ae3ce1838b7a8b974aa35070e4a</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>REQ-20250214-cto-ai-architecture-approval-execution-result</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-07-31T21:26:47.702+09:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CTO실</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>bench:S01:B00000</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>AWS·Azure·GCP, GPU 자체구축·클라우드 임차, SAP HANA·Oracle 비교 및 9개 영향 산출물의 갱신을 승인·기록한다. 클라우드 GPU 3년 TCO 12% 우위는 조건부 권고로 유지하며 비용·라이선스·보안·PoC·운영 책임 및 CTO실 최종 승인 전 최종 클라우드와 DB는 확정하지 않는다.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>AWS·Azure·GCP와 GPU 운영 방식 및 SAP HANA·Oracle을 비용·기능·보안·연계성·운영·확장성 기준으로 비교하고 TCO·민감도·PoC·승인 조건을 산출물에 반영한다.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>전사 AI 아키텍처 비교·선정안; AI Serving 하드웨어 검토서; 데이터베이스 선정 검토서; CTO실 의사결정 보고서; 요구사항 추적표; 보고 장표; TCO 비교표; 산출물 설계서</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>add,modify</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/673a4140a24bae1811ab32810cb89872fac73a7b</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>REQ-20250214-cto-ai-architecture-approval-execution-result-v4</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-07-31T12:53:11.248Z</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CTO실</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>bench:S01:B00000</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AWS·Azure·GCP, GPU 자체구축·클라우드 임차, SAP HANA·Oracle 비교와 TCO·PoC·보안·규정 준수·운영 책임 검증 항목을 산출물에 반영하며, 클라우드 GPU 3년 TCO 12% 우위는 조건부 권고로 유지한다. 최종 플랫폼·DB 선정은 검증 및 CTO실 승인 이후 확정한다.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>승인된 전사 AI 아키텍처 비교·선정, GPU Serving 하드웨어, SAP HANA·Oracle DB 검토 및 관련 추적·보고 산출물을 갱신한다.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>전사 AI 아키텍처 비교·선정안; AI Serving 하드웨어 검토서; 데이터베이스 선정 검토서; CTO실 의사결정 보고서; 요구사항 추적표 및 보고 장표; 산출물_설계서.docx; 요구사항_추적표.xlsx; 보고_장표.pptx</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>add; add; add; add; modify; modify; modify; modify</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/8951bd87d9d3b30ac3c5446b75f3b77517e2ad08</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>REQ-20250214-cto-ai-architecture-approval-execution-result-v7</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-07-31T22:11:06.033+09:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CTO실</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>bench:S01:B00001</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>승인된 5개 영향 산출물과 기성 문서 3종의 갱신 실행을 기록한다. 클라우드 GPU 12% TCO 우위는 조건부 권고로 유지하며 비용·라이선스·보안·규정 준수·PoC·운영 책임 검증과 CTO실 최종 승인 전에는 플랫폼·GPU 방식·DB를 확정하지 않는다.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>AWS·Azure·GCP 플랫폼, GPU 자체구축·클라우드 임차, SAP HANA·Oracle을 비용·보안·규정 준수·운영·성능·확장성·연계성 기준으로 비교하고 검증 게이트를 요구사항 추적표와 CTO실 보고서에 연결한다.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>전사 AI 아키텍처 비교·선정안; AI Serving 하드웨어 검토서; 데이터베이스 선정 검토서; CTO실 의사결정 보고서; 요구사항 추적표 및 경영진 보고 장표</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>add/modify</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/cc6f482ab80f056ae33962f2877282773b68b71c</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>REQ-20250214-cto-ai-architecture-approval-execution-result-v6</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-07-31T22:08:05.861+09:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CTO실</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>bench:S01:B00010</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>산출물 갱신 실행을 승인 결과로 기록하되 클라우드 GPU 3년 TCO 12% 우위는 조건부 권고로 유지하고 비용·라이선스·PoC·보안·운영 검증 및 CTO실 최종 승인 후 최종 아키텍처를 확정한다.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>AWS·Azure·GCP, GPU 자체구축·클라우드 임차, SAP HANA·Oracle 비교와 검증 게이트를 전사 AI 아키텍처 관련 산출물에 반영</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>전사 AI 아키텍처 비교·선정안; AI Serving 하드웨어 검토서; 데이터베이스 선정 검토서; CTO실 의사결정 보고서; 요구사항 추적표 및 보고 장표</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>modify</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/63709b2862514dcc7d33a08b0ad5cc898b5217ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>REQ-20250214-cto-ai-architecture-selection-approval</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-07-31T22:03:58.653+09:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CTO실</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>bench:S01:B00100</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>보완 조건부 승인. 전사 AI 아키텍처, GPU 인프라, 데이터베이스 비교 산출물과 CTO 의사결정 보고서를 추가·갱신하고, 클라우드 GPU의 12% TCO 우위는 조건부 권고로 유지한다. 최종 선정 전 비용·라이선스·규정 준수 근거, 교차 모듈 영향, 운영·탈출 계획 및 정량 PoC·벤치마크 게이트를 확정한다.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>AWS·Azure·GCP·GPU 자체구축/클라우드 임차·SAP HANA/Oracle 비교 및 CTO 의사결정 보고서 추가, 요구사항 추적표·경영진 보고 장표 수정</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>전사 AI 아키텍처 비교·선정안(add); AI Serving 하드웨어 검토서(add); 데이터베이스 선정 검토서(add); CTO실 의사결정 보고서(add); 요구사항 추적표 및 경영진 보고 장표(modify)</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>add/modify</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/b4596d0d09a7d11eb067547749763eaeeef3c33c</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>REQ-20250214-cto-ai-architecture-selection</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-07-31T21:04:49.005+09:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CTO실</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>bench:S01:B01000</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>전사 AI 아키텍처 비교·선정안, AI Serving 하드웨어 검토서, 데이터베이스 선정 검토서, CTO실 의사결정 보고서 및 요구사항 추적표를 갱신한다. 3년 TCO 기준 클라우드 GPU 12% 우위를 조건부 권고하되 비용·라이선스·PoC·벤치마크·규제 요건 검증 전 최종 클라우드와 DB를 확정하지 않는다.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>클라우드·GPU Serving·DB 비교 기준, 3년 TCO, 조건부 권고 및 최종 확정 전 검증 항목을 반영한다.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>전사 AI 아키텍처 비교·선정안; AI Serving 하드웨어 검토서; 데이터베이스 선정 검토서; CTO실 의사결정 보고서; 요구사항 추적표 및 보고 장표</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>add/modify</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>5</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/a7c52a9b948bf4f8e95700edab8526f7d639025d</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>REQ-20250214-cto-ai-architecture-approval-execution-result-v2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-07-31T12:30:02.815Z</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CTO실</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>bench:S01:B01000</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AWS·Azure·GCP, GPU 자체구축·클라우드 임차, SAP HANA·Oracle 비교 산출물과 CTO 의사결정·추적 산출물을 갱신했으며, 원천 TCO·민감도·중단 기준과 규제·운영·네트워크·MLOps·DR 검증 및 담당자·기한·PoC 승인 게이트 확정 전 최종 아키텍처 선정은 보류한다.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>승인된 전사 AI 아키텍처 비교·선정 범위를 산출물에 반영하고, 클라우드 GPU 3년 TCO 12% 우위를 조건부 권고로 기록하되 검증 완료 전 최종 클라우드·DB 확정을 보류한다.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>전사 AI 아키텍처 비교·선정안; AI Serving 하드웨어 검토서; 데이터베이스 선정 검토서; CTO실 의사결정 보고서; 요구사항 추적표 및 보고 장표</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>add; add; add; add; modify</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>5</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/61f52d9375634b089cd9fc967159cadee4aef5f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>REQ-20250214-cto-ai-architecture-selection</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-07-31T22:00:49.427+09:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CTO실</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>bench:S01:B01000</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>진행을 승인하되 클라우드 GPU 12% TCO 우위는 잠정·조건부 권고로 제한하고, 비용·라이선스·보안·운영·PoC 검증과 cross-module 영향 추적을 완료한 후 최종 플랫폼 및 DB를 확정한다.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>AWS·Azure·GCP 및 SAP HANA·Oracle 비교, GPU TCO 검증, PoC·보안·운영 선행 조건 반영</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>전사 AI 아키텍처 비교·선정안; AI Serving 하드웨어 검토서; 데이터베이스 선정 검토서; CTO실 의사결정 보고서; 요구사항 추적표 및 보고 장표</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>add,add,add,add,modify</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>5</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/936298833b71ecb10323acc65d44caa19bc18a91</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>REQ-20250214-cto-ai-architecture-approval-execution-result-v5</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-07-31T21:57:48.522+09:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CTO실</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>bench:S01:B10000</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AWS·Azure·GCP, GPU 자체구축·클라우드 임차, SAP HANA·Oracle 비교 및 관련 산출물 갱신을 완료한 것으로 기록한다. 클라우드 GPU 3년 TCO 12% 우위는 조건부 권고로 유지하며 PoC·벤치마크, 비용·라이선스·보안·규제·운영 책임 검증과 CTO실 최종 승인을 최종 확정 조건으로 둔다.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>AWS·Azure·GCP 비교·선정안; AI Serving 하드웨어 검토서; 데이터베이스 선정 검토서; CTO실 의사결정 보고서; 요구사항 추적표 및 보고 장표</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>modify</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>5</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/4f725eaefc643f3c8f3f47baf4a9f31811e5723b</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>REQ-20250214-cto-ai-architecture-approval-payload</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-07-31T21:08:52.844+09:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CTO실</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>bench:S01:B10101</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AWS·Azure·GCP, GPU 자체구축·클라우드 임차, SAP HANA·Oracle 비교와 관련 산출물 갱신을 승인한다. 클라우드 GPU의 3년 TCO 12% 우위는 조건부 권고로 기록하되 비용·보안·규제·라이선스·성능·PoC 검증 및 CTO실 최종 승인 전에는 최종 클라우드와 DB를 확정하지 않는다.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>전사 AI 아키텍처, AI Serving 하드웨어, 데이터베이스, CTO실 의사결정, 요구사항 추적표, 설계서, 보고 장표, TCO 비교표 갱신</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>전사 AI 아키텍처 비교·선정안; AI Serving 하드웨어 검토서; 데이터베이스 선정 검토서; CTO실 의사결정 보고서; 요구사항 추적표 및 보고 장표; 산출물_설계서.docx; 요구사항_추적표.xlsx; 보고_장표.pptx; TCO_비교표.xlsx</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>add/modify</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/c65cfc68d32450ffed72981cbb6a45305a4670ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>REQ-20250214-cto-ai-architecture-approval-execution-result-v3</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-07-31T21:33:04.173+09:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CTO실</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>bench:S01:B10101</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AWS·Azure·GCP, GPU 자체구축·클라우드 GPU 임차, SAP HANA·Oracle 비교 산출물과 관련 문서·추적표·보고 장표를 갱신한다. 클라우드 GPU 3년 TCO 12% 우위는 조건부 권고로 유지하며 원천 데이터 재현성, 법무·보안 검토, 모듈 간 영향 분석, PoC 임계값, 책임자·기한 및 CTO실 최종 승인 전 최종 클라우드·DB 확정은 보류한다.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>전사 AI 아키텍처 비교·선정안; AI Serving 하드웨어 검토서; 데이터베이스 선정 검토서; CTO실 의사결정 보고서; 요구사항 추적표 및 보고 장표; 산출물_설계서.docx; 요구사항_추적표.xlsx; 보고_장표.pptx; TCO_비교표.xlsx</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>add/modify</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>5</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/7911076d323e5b58da390d3be5c6e8decedb7e8b</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>REQ-20250214-cto-ai-architecture-approval-execution</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-07-31T21:12:49.903+09:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CTO실</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>bench:S01:B11111</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>비교·검토 산출물과 요구사항 추적표·보고 장표의 갱신을 승인한다. 단, 12% TCO 우위는 근거·민감도·손익분기 분석, 컴플라이언스 통제, PoC·벤치마크 기준 및 운영 SLA를 확정한 뒤 최종 아키텍처와 DB를 결정한다.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>AWS·Azure·GCP, GPU 운영 방식, SAP HANA·Oracle 비교와 비용·보안·규제·PoC·벤치마크 검증 조건을 반영한다.</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>전사 AI 아키텍처 비교·선정안; AI Serving 하드웨어 검토서; 데이터베이스 선정 검토서; CTO실 의사결정 보고서; 요구사항 추적표 및 보고 장장</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>add/modify</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>5</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/415c45e7e851ea942b4a25c151b54b6621815fbd</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>REQ-20250214-cto-ai-architecture-selection</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-07-31T21:35:51.302+09:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CTO실</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>bench:S01:B11111</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>AWS·Azure·GCP, GPU 자체구축·클라우드 임차, SAP HANA·Oracle을 비교하고 클라우드 GPU 3년 TCO 12% 우위를 검증 전 조건부 권고로 승인하되, 비용·라이선스·보안·책임모델·PoC 검증과 CTO실 최종 의사결정을 선행한다.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>클라우드 플랫폼, GPU 서빙 방식 및 데이터베이스를 비용·기술·보안·운영·확장성 기준으로 비교하고, 클라우드 GPU 3년 TCO 12% 우위를 조건부 권고로 추적한다.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>전사 AI 아키텍처 비교·선정안; AI Serving 하드웨어 검토서; 데이터베이스 선정 검토서; CTO실 의사결정 보고서; 요구사항 추적표 및 보고 장표</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>add,modify</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/203d21b88d74743da0f024143c103e60e068de09</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/scenarios/S01_enterprise_architecture/deliverables/TCO_벤더평가_시트.xlsx
+++ b/scenarios/S01_enterprise_architecture/deliverables/TCO_벤더평가_시트.xlsx
@@ -989,7 +989,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1734,6 +1734,56 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>REQ-20250214-cto-ai-architecture-approval-execution-result-v8</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-08-01T01:17:31.205+09:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CTO실</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>bench:S01:B10101</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>5개 영향 산출물과 기성 문서 3종의 갱신을 승인·완료로 기록하되, 클라우드 GPU 12% TCO 우위는 조건부 권고로 유지하고 비용·보안·라이선스·운영·PoC 검증 게이트 완료 전 최종 선정을 보류한다.</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>AWS·Azure·GCP, GPU 운영 방식, SAP HANA·Oracle 비교 및 비용·보안·규정 준수·운영·PoC 검증 게이트를 관련 산출물과 CTO실 의사결정에 연결한다.</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>전사 AI 아키텍처 비교·선정안; AI Serving 하드웨어 검토서; 데이터베이스 선정 검토서; CTO실 의사결정 보고서; 요구사항 추적표 및 경영진 보고 장표</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>add; add; add; add; modify</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>5</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>https://github.com/Abraxaspark91/n8n_termpjt/commit/10863a7a2a9d7dc83c1659cdf7dd72d26225fed5</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
